--- a/data/tiktok/data/2026-September-GSM-TT.xlsx
+++ b/data/tiktok/data/2026-September-GSM-TT.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C8BD3E-C7A6-4B10-8AE1-8D35832AF123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF4896B-5A60-4EC1-A3FD-E449A21D5113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="85">
   <si>
     <t>Ad name</t>
   </si>
@@ -136,12 +136,6 @@
     <t>Ended</t>
   </si>
   <si>
-    <t>Not delivered</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -157,6 +151,9 @@
     <t>Campaign name</t>
   </si>
   <si>
+    <t>2105 - Main Account - Video view</t>
+  </si>
+  <si>
     <t>2105 - สาขาเหล่านาดี - Video view</t>
   </si>
   <si>
@@ -196,9 +193,6 @@
     <t xml:space="preserve">2105 - Video View - KOLs </t>
   </si>
   <si>
-    <t>2105 - Main Account - Video view</t>
-  </si>
-  <si>
     <t>Spend</t>
   </si>
   <si>
@@ -211,52 +205,46 @@
     <t>997.21</t>
   </si>
   <si>
-    <t>998.66</t>
-  </si>
-  <si>
-    <t>1994.01</t>
-  </si>
-  <si>
-    <t>1994.89</t>
-  </si>
-  <si>
-    <t>1994.38</t>
+    <t>2000.00</t>
+  </si>
+  <si>
+    <t>1999.99</t>
+  </si>
+  <si>
+    <t>1999.89</t>
   </si>
   <si>
     <t>1999.88</t>
   </si>
   <si>
-    <t>1996.04</t>
-  </si>
-  <si>
-    <t>1997.29</t>
-  </si>
-  <si>
-    <t>1208.95</t>
+    <t>1999.98</t>
+  </si>
+  <si>
+    <t>1999.92</t>
+  </si>
+  <si>
+    <t>1291.23</t>
   </si>
   <si>
     <t>2500.00</t>
   </si>
   <si>
-    <t>2000.00</t>
-  </si>
-  <si>
-    <t>3989.36</t>
-  </si>
-  <si>
-    <t>3987.98</t>
+    <t>3999.88</t>
+  </si>
+  <si>
+    <t>3999.93</t>
   </si>
   <si>
     <t>2399.92</t>
   </si>
   <si>
-    <t>3989.07</t>
-  </si>
-  <si>
-    <t>3989.33</t>
-  </si>
-  <si>
-    <t>3988.59</t>
+    <t>3999.96</t>
+  </si>
+  <si>
+    <t>3999.94</t>
+  </si>
+  <si>
+    <t>3999.73</t>
   </si>
   <si>
     <t>Reach</t>
@@ -669,58 +657,58 @@
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -731,13 +719,13 @@
         <v>27</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F2" s="2">
         <v>47736</v>
@@ -773,16 +761,16 @@
         <v>10</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -793,13 +781,13 @@
         <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F3" s="2">
         <v>42392</v>
@@ -835,16 +823,16 @@
         <v>11</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -855,13 +843,13 @@
         <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2">
         <v>49359</v>
@@ -897,16 +885,16 @@
         <v>10</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -917,13 +905,13 @@
         <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="2">
         <v>41971</v>
@@ -959,16 +947,16 @@
         <v>6</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -976,25 +964,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" s="2">
-        <v>41866</v>
+        <v>41873</v>
       </c>
       <c r="G6" s="2">
-        <v>75186</v>
+        <v>75187</v>
       </c>
       <c r="H6" s="2">
-        <v>74140</v>
+        <v>74141</v>
       </c>
       <c r="I6" s="2">
         <v>9239</v>
@@ -1021,16 +1009,16 @@
         <v>8</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1041,13 +1029,13 @@
         <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2">
         <v>36771</v>
@@ -1083,16 +1071,16 @@
         <v>9</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1100,31 +1088,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2">
-        <v>42165</v>
+        <v>42333</v>
       </c>
       <c r="G8" s="2">
-        <v>74947</v>
+        <v>75044</v>
       </c>
       <c r="H8" s="2">
-        <v>73522</v>
+        <v>73619</v>
       </c>
       <c r="I8" s="2">
-        <v>7200</v>
+        <v>7213</v>
       </c>
       <c r="J8" s="2">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="K8" s="2">
         <v>60</v>
@@ -1145,16 +1133,16 @@
         <v>4</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1165,13 +1153,13 @@
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2">
         <v>18931</v>
@@ -1207,16 +1195,16 @@
         <v>11</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1224,34 +1212,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2">
-        <v>75870</v>
+        <v>76293</v>
       </c>
       <c r="G10" s="2">
-        <v>145424</v>
+        <v>145925</v>
       </c>
       <c r="H10" s="2">
-        <v>142154</v>
+        <v>142647</v>
       </c>
       <c r="I10" s="2">
-        <v>31683</v>
+        <v>31786</v>
       </c>
       <c r="J10" s="2">
-        <v>4225</v>
+        <v>4236</v>
       </c>
       <c r="K10" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -1269,16 +1257,16 @@
         <v>14</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1286,31 +1274,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F11" s="2">
-        <v>73800</v>
+        <v>74193</v>
       </c>
       <c r="G11" s="2">
-        <v>149021</v>
+        <v>149457</v>
       </c>
       <c r="H11" s="2">
-        <v>146960</v>
+        <v>147385</v>
       </c>
       <c r="I11" s="2">
-        <v>16069</v>
+        <v>16113</v>
       </c>
       <c r="J11" s="2">
-        <v>2162</v>
+        <v>2166</v>
       </c>
       <c r="K11" s="2">
         <v>73</v>
@@ -1331,16 +1319,16 @@
         <v>15</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1348,31 +1336,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F12" s="2">
-        <v>67397</v>
+        <v>67638</v>
       </c>
       <c r="G12" s="2">
-        <v>147214</v>
+        <v>147687</v>
       </c>
       <c r="H12" s="2">
-        <v>145234</v>
+        <v>145698</v>
       </c>
       <c r="I12" s="2">
-        <v>12849</v>
+        <v>12872</v>
       </c>
       <c r="J12" s="2">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="K12" s="2">
         <v>95</v>
@@ -1390,19 +1378,19 @@
         <v>156</v>
       </c>
       <c r="P12" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1413,13 +1401,13 @@
         <v>27</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F13" s="2">
         <v>68187</v>
@@ -1455,16 +1443,16 @@
         <v>14</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1472,31 +1460,31 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F14" s="2">
-        <v>69700</v>
+        <v>69868</v>
       </c>
       <c r="G14" s="2">
-        <v>139558</v>
+        <v>139725</v>
       </c>
       <c r="H14" s="2">
-        <v>137704</v>
+        <v>137865</v>
       </c>
       <c r="I14" s="2">
-        <v>30322</v>
+        <v>30361</v>
       </c>
       <c r="J14" s="2">
-        <v>3980</v>
+        <v>3987</v>
       </c>
       <c r="K14" s="2">
         <v>104</v>
@@ -1514,19 +1502,19 @@
         <v>127</v>
       </c>
       <c r="P14" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1534,34 +1522,34 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F15" s="2">
-        <v>75580</v>
+        <v>75851</v>
       </c>
       <c r="G15" s="2">
-        <v>146739</v>
+        <v>146959</v>
       </c>
       <c r="H15" s="2">
-        <v>143556</v>
+        <v>143773</v>
       </c>
       <c r="I15" s="2">
-        <v>22004</v>
+        <v>22025</v>
       </c>
       <c r="J15" s="2">
         <v>3311</v>
       </c>
       <c r="K15" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L15" s="2">
         <v>0</v>
@@ -1579,16 +1567,16 @@
         <v>22</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1596,61 +1584,61 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F16" s="2">
-        <v>1096</v>
+        <v>1140</v>
       </c>
       <c r="G16" s="2">
-        <v>1566</v>
+        <v>1629</v>
       </c>
       <c r="H16" s="2">
-        <v>1499</v>
+        <v>1562</v>
       </c>
       <c r="I16" s="2">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="J16" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K16" s="2">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L16" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="O16" s="2">
         <v>11</v>
       </c>
       <c r="P16" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1658,16 +1646,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F17" s="2">
         <v>3572</v>
@@ -1703,16 +1691,16 @@
         <v>84</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1720,16 +1708,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F18" s="2">
         <v>2909</v>
@@ -1765,16 +1753,16 @@
         <v>117</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1782,16 +1770,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F19" s="2">
         <v>2662</v>
@@ -1827,16 +1815,16 @@
         <v>113</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1847,13 +1835,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F20" s="2">
         <v>61617</v>
@@ -1889,16 +1877,16 @@
         <v>19</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1906,34 +1894,34 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2">
-        <v>99048</v>
+        <v>99273</v>
       </c>
       <c r="G21" s="2">
-        <v>281765</v>
+        <v>282629</v>
       </c>
       <c r="H21" s="2">
-        <v>275273</v>
+        <v>276118</v>
       </c>
       <c r="I21" s="2">
-        <v>41040</v>
+        <v>41134</v>
       </c>
       <c r="J21" s="2">
-        <v>5072</v>
+        <v>5081</v>
       </c>
       <c r="K21" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L21" s="2">
         <v>0</v>
@@ -1951,16 +1939,16 @@
         <v>28</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -1968,31 +1956,31 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F22" s="2">
-        <v>102229</v>
+        <v>102533</v>
       </c>
       <c r="G22" s="2">
-        <v>283636</v>
+        <v>284604</v>
       </c>
       <c r="H22" s="2">
-        <v>277619</v>
+        <v>278580</v>
       </c>
       <c r="I22" s="2">
-        <v>39510</v>
+        <v>39587</v>
       </c>
       <c r="J22" s="2">
-        <v>7649</v>
+        <v>7658</v>
       </c>
       <c r="K22" s="2">
         <v>300</v>
@@ -2013,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2030,16 +2018,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F23" s="2">
         <v>74915</v>
@@ -2075,16 +2063,16 @@
         <v>25</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2092,31 +2080,31 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F24" s="2">
-        <v>103046</v>
+        <v>103227</v>
       </c>
       <c r="G24" s="2">
-        <v>288509</v>
+        <v>289411</v>
       </c>
       <c r="H24" s="2">
-        <v>283000</v>
+        <v>283888</v>
       </c>
       <c r="I24" s="2">
-        <v>26080</v>
+        <v>26130</v>
       </c>
       <c r="J24" s="2">
-        <v>7755</v>
+        <v>7766</v>
       </c>
       <c r="K24" s="2">
         <v>136</v>
@@ -2137,16 +2125,16 @@
         <v>22</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2154,34 +2142,34 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F25" s="2">
-        <v>100333</v>
+        <v>100443</v>
       </c>
       <c r="G25" s="2">
-        <v>290468</v>
+        <v>291340</v>
       </c>
       <c r="H25" s="2">
-        <v>286372</v>
+        <v>287234</v>
       </c>
       <c r="I25" s="2">
-        <v>26869</v>
+        <v>26921</v>
       </c>
       <c r="J25" s="2">
-        <v>3633</v>
+        <v>3642</v>
       </c>
       <c r="K25" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L25" s="2">
         <v>0</v>
@@ -2193,22 +2181,22 @@
         <v>14</v>
       </c>
       <c r="O25" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P25" s="2">
         <v>29</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2216,31 +2204,31 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F26" s="2">
-        <v>98087</v>
+        <v>98226</v>
       </c>
       <c r="G26" s="2">
-        <v>284737</v>
+        <v>285635</v>
       </c>
       <c r="H26" s="2">
-        <v>278989</v>
+        <v>279866</v>
       </c>
       <c r="I26" s="2">
-        <v>19683</v>
+        <v>19731</v>
       </c>
       <c r="J26" s="2">
-        <v>4865</v>
+        <v>4880</v>
       </c>
       <c r="K26" s="2">
         <v>120</v>
@@ -2255,22 +2243,22 @@
         <v>10</v>
       </c>
       <c r="O26" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P26" s="2">
         <v>25</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
@@ -2281,13 +2269,13 @@
         <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F27" s="2">
         <v>68077</v>
@@ -2323,16 +2311,16 @@
         <v>33</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
